--- a/static/data/exports/Retro_PY_AE_2026.xlsx
+++ b/static/data/exports/Retro_PY_AE_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,16 +578,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>56</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>57</v>
@@ -650,16 +653,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>54</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>57</v>
@@ -722,16 +728,19 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P4" t="n">
         <v>44</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>57</v>
@@ -794,16 +803,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>51</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>57</v>
@@ -864,6 +876,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
       <c r="R6" t="n">
         <v>57</v>
       </c>
@@ -925,16 +940,19 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P7" t="n">
         <v>29</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>57</v>
@@ -997,16 +1015,19 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>47</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>57</v>
@@ -1069,16 +1090,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>42</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>57</v>
@@ -1141,16 +1165,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>37</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>57</v>
@@ -1213,16 +1240,19 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>54</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>57</v>
@@ -1285,16 +1315,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>67</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>57</v>
@@ -1357,16 +1390,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>38</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>57</v>
@@ -1434,11 +1470,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P14" t="n">
         <v>53</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>57</v>
@@ -1506,11 +1545,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P15" t="n">
         <v>43</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>57</v>
@@ -1578,11 +1620,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>57</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>57</v>
@@ -1650,11 +1695,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P17" t="n">
         <v>49</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>57</v>
@@ -1722,11 +1770,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>30</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>57</v>
@@ -1794,11 +1845,14 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>47</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>57</v>
@@ -1866,11 +1920,14 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P20" t="n">
         <v>47</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>57</v>
@@ -1931,6 +1988,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
       <c r="R21" t="n">
         <v>57</v>
       </c>
@@ -1997,11 +2057,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P22" t="n">
         <v>37</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>57</v>
@@ -2069,11 +2132,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P23" t="n">
         <v>65</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>57</v>
@@ -2141,11 +2207,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P24" t="n">
         <v>53</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>57</v>
@@ -2213,11 +2282,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P25" t="n">
         <v>34</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>57</v>
@@ -2285,11 +2357,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P26" t="n">
         <v>50</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>57</v>
@@ -2357,11 +2432,14 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P27" t="n">
         <v>60</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>57</v>
@@ -2429,11 +2507,14 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P28" t="n">
         <v>45</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>57</v>
@@ -2501,11 +2582,14 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P29" t="n">
         <v>30</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>57</v>
@@ -2566,6 +2650,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
       <c r="R30" t="n">
         <v>57</v>
       </c>
@@ -2632,11 +2719,14 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P31" t="n">
         <v>65</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>57</v>
@@ -2699,16 +2789,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P32" t="n">
         <v>75</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>57</v>
@@ -2771,16 +2864,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P33" t="n">
         <v>74</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>57</v>
@@ -2843,16 +2939,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P34" t="n">
         <v>36</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>57</v>
@@ -2915,16 +3014,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P35" t="n">
         <v>45</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>57</v>
@@ -2987,16 +3089,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P36" t="n">
         <v>43</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>57</v>
@@ -3057,6 +3162,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
       <c r="R37" t="n">
         <v>57</v>
       </c>
@@ -3118,16 +3226,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P38" t="n">
         <v>38</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>57</v>
@@ -3190,16 +3301,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P39" t="n">
         <v>60</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>57</v>
@@ -3262,16 +3376,19 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P40" t="n">
         <v>42</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>57</v>
@@ -3334,16 +3451,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P41" t="n">
         <v>57</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>57</v>
@@ -3406,16 +3526,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P42" t="n">
         <v>48</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>57</v>
@@ -3478,16 +3601,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P43" t="n">
         <v>59</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>57</v>
@@ -3550,16 +3676,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P44" t="n">
         <v>42</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>57</v>
@@ -3622,16 +3751,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P45" t="n">
         <v>50</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>57</v>
@@ -3692,6 +3824,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
       <c r="R46" t="n">
         <v>57</v>
       </c>
@@ -3753,16 +3888,19 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P47" t="n">
         <v>46</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>57</v>
@@ -3825,16 +3963,19 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P48" t="n">
         <v>32</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>57</v>
@@ -3897,16 +4038,19 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P49" t="n">
         <v>65</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>57</v>
@@ -3969,16 +4113,19 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P50" t="n">
         <v>38</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>57</v>
@@ -4041,16 +4188,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P51" t="n">
         <v>49</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>57</v>
@@ -4113,16 +4263,19 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P52" t="n">
         <v>36</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>57</v>
@@ -4185,16 +4338,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P53" t="n">
         <v>57</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>57</v>
@@ -4257,16 +4413,19 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P54" t="n">
         <v>49</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>57</v>
@@ -4329,16 +4488,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P55" t="n">
         <v>37</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>57</v>
@@ -4401,16 +4563,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P56" t="n">
         <v>42</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>57</v>
@@ -4473,16 +4638,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P57" t="n">
         <v>45</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>57</v>
@@ -4545,16 +4713,19 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P58" t="n">
         <v>65</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>57</v>
@@ -4617,16 +4788,19 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P59" t="n">
         <v>43</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>57</v>
@@ -4689,16 +4863,19 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P60" t="n">
         <v>39</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>57</v>
@@ -4761,16 +4938,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P61" t="n">
         <v>40</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>57</v>
@@ -4833,16 +5013,19 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P62" t="n">
         <v>66</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>57</v>
@@ -4905,16 +5088,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P63" t="n">
         <v>39</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>57</v>
@@ -4975,6 +5161,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
       <c r="R64" t="n">
         <v>57</v>
       </c>
@@ -5036,16 +5225,19 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P65" t="n">
         <v>48</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>57</v>
@@ -5108,16 +5300,19 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P66" t="n">
         <v>46</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>57</v>
@@ -5180,16 +5375,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P67" t="n">
         <v>63</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>57</v>
@@ -5252,16 +5450,19 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P68" t="n">
         <v>28</v>
+      </c>
+      <c r="Q68" t="b">
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>57</v>
@@ -5324,16 +5525,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P69" t="n">
         <v>31</v>
+      </c>
+      <c r="Q69" t="b">
+        <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>57</v>
@@ -5396,16 +5600,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P70" t="n">
         <v>46</v>
+      </c>
+      <c r="Q70" t="b">
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>57</v>
@@ -5468,16 +5675,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P71" t="n">
         <v>47</v>
+      </c>
+      <c r="Q71" t="b">
+        <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>57</v>
@@ -5540,16 +5750,19 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P72" t="n">
         <v>51</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>57</v>
@@ -5612,16 +5825,19 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P73" t="n">
         <v>45</v>
+      </c>
+      <c r="Q73" t="b">
+        <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>57</v>
@@ -5684,16 +5900,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P74" t="n">
         <v>45</v>
+      </c>
+      <c r="Q74" t="b">
+        <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>57</v>
@@ -5754,6 +5973,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q75" t="b">
+        <v>0</v>
+      </c>
       <c r="R75" t="n">
         <v>57</v>
       </c>
@@ -5815,16 +6037,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P76" t="n">
         <v>70</v>
+      </c>
+      <c r="Q76" t="b">
+        <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>57</v>
@@ -5887,16 +6112,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P77" t="n">
         <v>45</v>
+      </c>
+      <c r="Q77" t="b">
+        <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>57</v>
@@ -5959,16 +6187,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P78" t="n">
         <v>51</v>
+      </c>
+      <c r="Q78" t="b">
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>57</v>
@@ -6031,16 +6262,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P79" t="n">
         <v>43</v>
+      </c>
+      <c r="Q79" t="b">
+        <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>57</v>
@@ -6103,16 +6337,19 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P80" t="n">
         <v>61</v>
+      </c>
+      <c r="Q80" t="b">
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>57</v>
@@ -6175,16 +6412,19 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P81" t="n">
         <v>58</v>
+      </c>
+      <c r="Q81" t="b">
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>57</v>
@@ -6247,16 +6487,19 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P82" t="n">
         <v>46</v>
+      </c>
+      <c r="Q82" t="b">
+        <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>57</v>
@@ -6319,16 +6562,19 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P83" t="n">
         <v>55</v>
+      </c>
+      <c r="Q83" t="b">
+        <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>57</v>
@@ -6391,16 +6637,19 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P84" t="n">
         <v>53</v>
+      </c>
+      <c r="Q84" t="b">
+        <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>57</v>
@@ -6461,6 +6710,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q85" t="b">
+        <v>0</v>
+      </c>
       <c r="R85" t="n">
         <v>57</v>
       </c>
@@ -6522,16 +6774,19 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P86" t="n">
         <v>38</v>
+      </c>
+      <c r="Q86" t="b">
+        <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>57</v>
@@ -6594,16 +6849,19 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P87" t="n">
         <v>68</v>
+      </c>
+      <c r="Q87" t="b">
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>57</v>
@@ -6666,16 +6924,19 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P88" t="n">
         <v>51</v>
+      </c>
+      <c r="Q88" t="b">
+        <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>57</v>
@@ -6738,16 +6999,19 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P89" t="n">
         <v>75</v>
+      </c>
+      <c r="Q89" t="b">
+        <v>1</v>
       </c>
       <c r="R89" t="n">
         <v>57</v>
@@ -6810,16 +7074,19 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P90" t="n">
         <v>49</v>
+      </c>
+      <c r="Q90" t="b">
+        <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>57</v>
@@ -6882,16 +7149,19 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P91" t="n">
         <v>54</v>
+      </c>
+      <c r="Q91" t="b">
+        <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>57</v>
@@ -6954,16 +7224,19 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P92" t="n">
         <v>75</v>
+      </c>
+      <c r="Q92" t="b">
+        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>57</v>
@@ -7026,16 +7299,19 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P93" t="n">
         <v>40</v>
+      </c>
+      <c r="Q93" t="b">
+        <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>57</v>
@@ -7096,6 +7372,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q94" t="b">
+        <v>0</v>
+      </c>
       <c r="R94" t="n">
         <v>57</v>
       </c>
@@ -7157,16 +7436,19 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P95" t="n">
         <v>55</v>
+      </c>
+      <c r="Q95" t="b">
+        <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>57</v>
@@ -7229,16 +7511,19 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P96" t="n">
         <v>67</v>
+      </c>
+      <c r="Q96" t="b">
+        <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>57</v>
@@ -7301,16 +7586,19 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P97" t="n">
         <v>30</v>
+      </c>
+      <c r="Q97" t="b">
+        <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>57</v>
@@ -7373,16 +7661,19 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P98" t="n">
         <v>37</v>
+      </c>
+      <c r="Q98" t="b">
+        <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>57</v>
@@ -7445,16 +7736,19 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P99" t="n">
         <v>62</v>
+      </c>
+      <c r="Q99" t="b">
+        <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>57</v>
@@ -7517,16 +7811,19 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P100" t="n">
         <v>37</v>
+      </c>
+      <c r="Q100" t="b">
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>57</v>
@@ -7589,16 +7886,19 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P101" t="n">
         <v>68</v>
+      </c>
+      <c r="Q101" t="b">
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>57</v>
@@ -7661,16 +7961,19 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P102" t="n">
         <v>39</v>
+      </c>
+      <c r="Q102" t="b">
+        <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>57</v>
@@ -7738,11 +8041,14 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P103" t="n">
         <v>41</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>57</v>
@@ -7803,6 +8109,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q104" t="b">
+        <v>0</v>
+      </c>
       <c r="R104" t="n">
         <v>57</v>
       </c>
@@ -7864,16 +8173,19 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P105" t="n">
         <v>52</v>
+      </c>
+      <c r="Q105" t="b">
+        <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>57</v>
@@ -7936,16 +8248,19 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P106" t="n">
         <v>43</v>
+      </c>
+      <c r="Q106" t="b">
+        <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>57</v>
@@ -8008,16 +8323,19 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P107" t="n">
         <v>46</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>57</v>
@@ -8080,16 +8398,19 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P108" t="n">
         <v>34</v>
+      </c>
+      <c r="Q108" t="b">
+        <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>57</v>
@@ -8152,16 +8473,19 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P109" t="n">
         <v>54</v>
+      </c>
+      <c r="Q109" t="b">
+        <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>57</v>
@@ -8224,16 +8548,19 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P110" t="n">
         <v>50</v>
+      </c>
+      <c r="Q110" t="b">
+        <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>57</v>
@@ -8296,16 +8623,19 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P111" t="n">
         <v>74</v>
+      </c>
+      <c r="Q111" t="b">
+        <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>57</v>
@@ -8368,16 +8698,19 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P112" t="n">
         <v>52</v>
+      </c>
+      <c r="Q112" t="b">
+        <v>1</v>
       </c>
       <c r="R112" t="n">
         <v>57</v>
@@ -8440,16 +8773,19 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P113" t="n">
         <v>56</v>
+      </c>
+      <c r="Q113" t="b">
+        <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>57</v>
@@ -8512,16 +8848,19 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P114" t="n">
         <v>35</v>
+      </c>
+      <c r="Q114" t="b">
+        <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>57</v>
@@ -8584,16 +8923,19 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P115" t="n">
         <v>63</v>
+      </c>
+      <c r="Q115" t="b">
+        <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>57</v>
@@ -8654,6 +8996,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q116" t="b">
+        <v>0</v>
+      </c>
       <c r="R116" t="n">
         <v>57</v>
       </c>
@@ -8715,16 +9060,19 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P117" t="n">
         <v>42</v>
+      </c>
+      <c r="Q117" t="b">
+        <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>57</v>
@@ -8787,16 +9135,19 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P118" t="n">
         <v>42</v>
+      </c>
+      <c r="Q118" t="b">
+        <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>57</v>
@@ -8859,16 +9210,19 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P119" t="n">
         <v>50</v>
+      </c>
+      <c r="Q119" t="b">
+        <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>57</v>
@@ -8931,16 +9285,19 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P120" t="n">
         <v>54</v>
+      </c>
+      <c r="Q120" t="b">
+        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>57</v>
@@ -9008,11 +9365,14 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P121" t="n">
         <v>40</v>
+      </c>
+      <c r="Q121" t="b">
+        <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>57</v>
@@ -9075,16 +9435,19 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P122" t="n">
         <v>59</v>
+      </c>
+      <c r="Q122" t="b">
+        <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>57</v>
@@ -9147,16 +9510,19 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P123" t="n">
         <v>50</v>
+      </c>
+      <c r="Q123" t="b">
+        <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>57</v>
@@ -9219,16 +9585,19 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P124" t="n">
         <v>48</v>
+      </c>
+      <c r="Q124" t="b">
+        <v>1</v>
       </c>
       <c r="R124" t="n">
         <v>57</v>
@@ -9291,16 +9660,19 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P125" t="n">
         <v>45</v>
+      </c>
+      <c r="Q125" t="b">
+        <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>57</v>
@@ -9363,16 +9735,19 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P126" t="n">
         <v>62</v>
+      </c>
+      <c r="Q126" t="b">
+        <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>57</v>
@@ -9435,16 +9810,19 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P127" t="n">
         <v>41</v>
+      </c>
+      <c r="Q127" t="b">
+        <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>57</v>
@@ -9505,6 +9883,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q128" t="b">
+        <v>0</v>
+      </c>
       <c r="R128" t="n">
         <v>57</v>
       </c>
@@ -9566,16 +9947,19 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P129" t="n">
         <v>41</v>
+      </c>
+      <c r="Q129" t="b">
+        <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>57</v>
@@ -9638,16 +10022,19 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P130" t="n">
         <v>61</v>
+      </c>
+      <c r="Q130" t="b">
+        <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>57</v>
@@ -9710,16 +10097,19 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P131" t="n">
         <v>44</v>
+      </c>
+      <c r="Q131" t="b">
+        <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>57</v>
@@ -9782,16 +10172,19 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P132" t="n">
         <v>52</v>
+      </c>
+      <c r="Q132" t="b">
+        <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>57</v>
@@ -9854,16 +10247,19 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P133" t="n">
         <v>44</v>
+      </c>
+      <c r="Q133" t="b">
+        <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>57</v>
@@ -9926,16 +10322,19 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P134" t="n">
         <v>54</v>
+      </c>
+      <c r="Q134" t="b">
+        <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>57</v>
@@ -9998,16 +10397,19 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P135" t="n">
         <v>39</v>
+      </c>
+      <c r="Q135" t="b">
+        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>57</v>
@@ -10070,16 +10472,19 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P136" t="n">
         <v>36</v>
+      </c>
+      <c r="Q136" t="b">
+        <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>57</v>
@@ -10140,6 +10545,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q137" t="b">
+        <v>0</v>
+      </c>
       <c r="R137" t="n">
         <v>57</v>
       </c>
@@ -10206,11 +10614,14 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P138" t="n">
         <v>44</v>
+      </c>
+      <c r="Q138" t="b">
+        <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>57</v>
@@ -10273,16 +10684,19 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P139" t="n">
         <v>64</v>
+      </c>
+      <c r="Q139" t="b">
+        <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>57</v>
@@ -10345,16 +10759,19 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P140" t="n">
         <v>43</v>
+      </c>
+      <c r="Q140" t="b">
+        <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>57</v>
@@ -10417,16 +10834,19 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P141" t="n">
         <v>34</v>
+      </c>
+      <c r="Q141" t="b">
+        <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>57</v>
@@ -10489,16 +10909,19 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P142" t="n">
         <v>46</v>
+      </c>
+      <c r="Q142" t="b">
+        <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>57</v>
@@ -10561,16 +10984,19 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P143" t="n">
         <v>27</v>
+      </c>
+      <c r="Q143" t="b">
+        <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>57</v>
@@ -10633,16 +11059,19 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P144" t="n">
         <v>64</v>
+      </c>
+      <c r="Q144" t="b">
+        <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>57</v>
@@ -10705,16 +11134,19 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P145" t="n">
         <v>62</v>
+      </c>
+      <c r="Q145" t="b">
+        <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>57</v>
@@ -10777,16 +11209,19 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P146" t="n">
         <v>51</v>
+      </c>
+      <c r="Q146" t="b">
+        <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>57</v>
@@ -10849,16 +11284,19 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P147" t="n">
         <v>29</v>
+      </c>
+      <c r="Q147" t="b">
+        <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>57</v>
@@ -10919,6 +11357,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q148" t="b">
+        <v>0</v>
+      </c>
       <c r="R148" t="n">
         <v>57</v>
       </c>
@@ -10980,16 +11421,19 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P149" t="n">
         <v>65</v>
+      </c>
+      <c r="Q149" t="b">
+        <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>57</v>
@@ -11052,16 +11496,19 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P150" t="n">
         <v>41</v>
+      </c>
+      <c r="Q150" t="b">
+        <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>57</v>
@@ -11124,16 +11571,19 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P151" t="n">
         <v>68</v>
+      </c>
+      <c r="Q151" t="b">
+        <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>57</v>
@@ -11196,16 +11646,19 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P152" t="n">
         <v>46</v>
+      </c>
+      <c r="Q152" t="b">
+        <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>57</v>
@@ -11268,16 +11721,19 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P153" t="n">
         <v>61</v>
+      </c>
+      <c r="Q153" t="b">
+        <v>1</v>
       </c>
       <c r="R153" t="n">
         <v>57</v>
@@ -11345,11 +11801,14 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P154" t="n">
         <v>42</v>
+      </c>
+      <c r="Q154" t="b">
+        <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>57</v>
@@ -11410,6 +11869,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q155" t="b">
+        <v>0</v>
+      </c>
       <c r="R155" t="n">
         <v>57</v>
       </c>
@@ -11471,16 +11933,19 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P156" t="n">
         <v>43</v>
+      </c>
+      <c r="Q156" t="b">
+        <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>57</v>
@@ -11543,16 +12008,19 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P157" t="n">
         <v>37</v>
+      </c>
+      <c r="Q157" t="b">
+        <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>57</v>
@@ -11615,16 +12083,19 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P158" t="n">
         <v>61</v>
+      </c>
+      <c r="Q158" t="b">
+        <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>57</v>
@@ -11687,16 +12158,19 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P159" t="n">
         <v>51</v>
+      </c>
+      <c r="Q159" t="b">
+        <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>57</v>
@@ -11759,16 +12233,19 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P160" t="n">
         <v>55</v>
+      </c>
+      <c r="Q160" t="b">
+        <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>57</v>
@@ -11831,16 +12308,19 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P161" t="n">
         <v>28</v>
+      </c>
+      <c r="Q161" t="b">
+        <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>57</v>
@@ -11901,6 +12381,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q162" t="b">
+        <v>0</v>
+      </c>
       <c r="R162" t="n">
         <v>57</v>
       </c>
@@ -11962,16 +12445,19 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P163" t="n">
         <v>50</v>
+      </c>
+      <c r="Q163" t="b">
+        <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>57</v>
@@ -12034,16 +12520,19 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P164" t="n">
         <v>40</v>
+      </c>
+      <c r="Q164" t="b">
+        <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>57</v>
@@ -12106,16 +12595,19 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P165" t="n">
         <v>50</v>
+      </c>
+      <c r="Q165" t="b">
+        <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>57</v>
@@ -12178,16 +12670,19 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P166" t="n">
         <v>30</v>
+      </c>
+      <c r="Q166" t="b">
+        <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>57</v>
@@ -12250,16 +12745,19 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P167" t="n">
         <v>44</v>
+      </c>
+      <c r="Q167" t="b">
+        <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>57</v>
@@ -12322,16 +12820,19 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P168" t="n">
         <v>37</v>
+      </c>
+      <c r="Q168" t="b">
+        <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>57</v>
@@ -12394,16 +12895,19 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P169" t="n">
         <v>41</v>
+      </c>
+      <c r="Q169" t="b">
+        <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>57</v>
@@ -12466,16 +12970,19 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P170" t="n">
         <v>64</v>
+      </c>
+      <c r="Q170" t="b">
+        <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>57</v>
@@ -12538,16 +13045,19 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P171" t="n">
         <v>50</v>
+      </c>
+      <c r="Q171" t="b">
+        <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>57</v>
@@ -12610,16 +13120,19 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P172" t="n">
         <v>59</v>
+      </c>
+      <c r="Q172" t="b">
+        <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>57</v>
@@ -12682,16 +13195,19 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P173" t="n">
         <v>65</v>
+      </c>
+      <c r="Q173" t="b">
+        <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>57</v>
@@ -12754,16 +13270,19 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P174" t="n">
         <v>30</v>
+      </c>
+      <c r="Q174" t="b">
+        <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>57</v>
@@ -12826,16 +13345,19 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P175" t="n">
         <v>54</v>
+      </c>
+      <c r="Q175" t="b">
+        <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>57</v>
@@ -12898,16 +13420,19 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P176" t="n">
         <v>59</v>
+      </c>
+      <c r="Q176" t="b">
+        <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>57</v>
@@ -12968,6 +13493,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q177" t="b">
+        <v>0</v>
+      </c>
       <c r="R177" t="n">
         <v>57</v>
       </c>
@@ -13029,16 +13557,19 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P178" t="n">
         <v>43</v>
+      </c>
+      <c r="Q178" t="b">
+        <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>57</v>
@@ -13101,16 +13632,19 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P179" t="n">
         <v>37</v>
+      </c>
+      <c r="Q179" t="b">
+        <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>57</v>
@@ -13173,16 +13707,19 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P180" t="n">
         <v>74</v>
+      </c>
+      <c r="Q180" t="b">
+        <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>57</v>
@@ -13245,16 +13782,19 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P181" t="n">
         <v>46</v>
+      </c>
+      <c r="Q181" t="b">
+        <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>57</v>
@@ -13317,16 +13857,19 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P182" t="n">
         <v>43</v>
+      </c>
+      <c r="Q182" t="b">
+        <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>57</v>
@@ -13389,16 +13932,19 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P183" t="n">
         <v>67</v>
+      </c>
+      <c r="Q183" t="b">
+        <v>0</v>
       </c>
       <c r="R183" t="n">
         <v>57</v>
@@ -13461,16 +14007,19 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P184" t="n">
         <v>48</v>
+      </c>
+      <c r="Q184" t="b">
+        <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>57</v>
@@ -13533,16 +14082,19 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P185" t="n">
         <v>66</v>
+      </c>
+      <c r="Q185" t="b">
+        <v>0</v>
       </c>
       <c r="R185" t="n">
         <v>57</v>
@@ -13605,16 +14157,19 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P186" t="n">
         <v>36</v>
+      </c>
+      <c r="Q186" t="b">
+        <v>0</v>
       </c>
       <c r="R186" t="n">
         <v>57</v>
@@ -13677,16 +14232,19 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P187" t="n">
         <v>60</v>
+      </c>
+      <c r="Q187" t="b">
+        <v>0</v>
       </c>
       <c r="R187" t="n">
         <v>57</v>
@@ -13749,16 +14307,19 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P188" t="n">
         <v>46</v>
+      </c>
+      <c r="Q188" t="b">
+        <v>1</v>
       </c>
       <c r="R188" t="n">
         <v>57</v>
@@ -13821,16 +14382,19 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P189" t="n">
         <v>41</v>
+      </c>
+      <c r="Q189" t="b">
+        <v>0</v>
       </c>
       <c r="R189" t="n">
         <v>57</v>
@@ -13893,16 +14457,19 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P190" t="n">
         <v>33</v>
+      </c>
+      <c r="Q190" t="b">
+        <v>0</v>
       </c>
       <c r="R190" t="n">
         <v>57</v>
@@ -13965,16 +14532,19 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P191" t="n">
         <v>43</v>
+      </c>
+      <c r="Q191" t="b">
+        <v>0</v>
       </c>
       <c r="R191" t="n">
         <v>57</v>
@@ -14035,6 +14605,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q192" t="b">
+        <v>0</v>
+      </c>
       <c r="R192" t="n">
         <v>57</v>
       </c>
@@ -14096,16 +14669,19 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P193" t="n">
         <v>71</v>
+      </c>
+      <c r="Q193" t="b">
+        <v>0</v>
       </c>
       <c r="R193" t="n">
         <v>57</v>
@@ -14168,16 +14744,19 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P194" t="n">
         <v>42</v>
+      </c>
+      <c r="Q194" t="b">
+        <v>0</v>
       </c>
       <c r="R194" t="n">
         <v>57</v>
@@ -14240,16 +14819,19 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P195" t="n">
         <v>35</v>
+      </c>
+      <c r="Q195" t="b">
+        <v>0</v>
       </c>
       <c r="R195" t="n">
         <v>57</v>
@@ -14312,16 +14894,19 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P196" t="n">
         <v>31</v>
+      </c>
+      <c r="Q196" t="b">
+        <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>57</v>
@@ -14384,16 +14969,19 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P197" t="n">
         <v>60</v>
+      </c>
+      <c r="Q197" t="b">
+        <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>57</v>
@@ -14461,11 +15049,14 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P198" t="n">
         <v>65</v>
+      </c>
+      <c r="Q198" t="b">
+        <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>57</v>
@@ -14528,16 +15119,19 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P199" t="n">
         <v>36</v>
+      </c>
+      <c r="Q199" t="b">
+        <v>0</v>
       </c>
       <c r="R199" t="n">
         <v>57</v>
@@ -14600,16 +15194,19 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P200" t="n">
         <v>40</v>
+      </c>
+      <c r="Q200" t="b">
+        <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>57</v>
@@ -14672,16 +15269,19 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P201" t="n">
         <v>33</v>
+      </c>
+      <c r="Q201" t="b">
+        <v>0</v>
       </c>
       <c r="R201" t="n">
         <v>57</v>
@@ -14744,16 +15344,19 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P202" t="n">
         <v>49</v>
+      </c>
+      <c r="Q202" t="b">
+        <v>0</v>
       </c>
       <c r="R202" t="n">
         <v>57</v>
@@ -14816,16 +15419,19 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P203" t="n">
         <v>55</v>
+      </c>
+      <c r="Q203" t="b">
+        <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>57</v>
@@ -14888,16 +15494,19 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P204" t="n">
         <v>56</v>
+      </c>
+      <c r="Q204" t="b">
+        <v>0</v>
       </c>
       <c r="R204" t="n">
         <v>57</v>
@@ -14960,16 +15569,19 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P205" t="n">
         <v>32</v>
+      </c>
+      <c r="Q205" t="b">
+        <v>0</v>
       </c>
       <c r="R205" t="n">
         <v>57</v>
@@ -15030,6 +15642,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q206" t="b">
+        <v>0</v>
+      </c>
       <c r="R206" t="n">
         <v>57</v>
       </c>
@@ -15091,16 +15706,19 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P207" t="n">
         <v>49</v>
+      </c>
+      <c r="Q207" t="b">
+        <v>0</v>
       </c>
       <c r="R207" t="n">
         <v>57</v>
@@ -15163,16 +15781,19 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P208" t="n">
         <v>45</v>
+      </c>
+      <c r="Q208" t="b">
+        <v>0</v>
       </c>
       <c r="R208" t="n">
         <v>57</v>
@@ -15235,16 +15856,19 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P209" t="n">
         <v>33</v>
+      </c>
+      <c r="Q209" t="b">
+        <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>57</v>
@@ -15307,16 +15931,19 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P210" t="n">
         <v>39</v>
+      </c>
+      <c r="Q210" t="b">
+        <v>0</v>
       </c>
       <c r="R210" t="n">
         <v>57</v>
@@ -15379,16 +16006,19 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P211" t="n">
         <v>29</v>
+      </c>
+      <c r="Q211" t="b">
+        <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>57</v>
@@ -15451,16 +16081,19 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P212" t="n">
         <v>60</v>
+      </c>
+      <c r="Q212" t="b">
+        <v>0</v>
       </c>
       <c r="R212" t="n">
         <v>57</v>
@@ -15523,16 +16156,19 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P213" t="n">
         <v>40</v>
+      </c>
+      <c r="Q213" t="b">
+        <v>0</v>
       </c>
       <c r="R213" t="n">
         <v>57</v>
@@ -15595,16 +16231,19 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P214" t="n">
         <v>65</v>
+      </c>
+      <c r="Q214" t="b">
+        <v>0</v>
       </c>
       <c r="R214" t="n">
         <v>57</v>
@@ -15667,16 +16306,19 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P215" t="n">
         <v>61</v>
+      </c>
+      <c r="Q215" t="b">
+        <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>57</v>
@@ -15739,16 +16381,19 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P216" t="n">
         <v>53</v>
+      </c>
+      <c r="Q216" t="b">
+        <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>57</v>
@@ -15811,16 +16456,19 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P217" t="n">
         <v>39</v>
+      </c>
+      <c r="Q217" t="b">
+        <v>0</v>
       </c>
       <c r="R217" t="n">
         <v>57</v>
@@ -15883,16 +16531,19 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P218" t="n">
         <v>44</v>
+      </c>
+      <c r="Q218" t="b">
+        <v>0</v>
       </c>
       <c r="R218" t="n">
         <v>57</v>
@@ -15953,6 +16604,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q219" t="b">
+        <v>0</v>
+      </c>
       <c r="R219" t="n">
         <v>57</v>
       </c>
@@ -16014,16 +16668,19 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P220" t="n">
         <v>34</v>
+      </c>
+      <c r="Q220" t="b">
+        <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>57</v>
@@ -16086,16 +16743,19 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P221" t="n">
         <v>50</v>
+      </c>
+      <c r="Q221" t="b">
+        <v>0</v>
       </c>
       <c r="R221" t="n">
         <v>57</v>
@@ -16158,16 +16818,19 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P222" t="n">
         <v>45</v>
+      </c>
+      <c r="Q222" t="b">
+        <v>0</v>
       </c>
       <c r="R222" t="n">
         <v>57</v>
@@ -16235,11 +16898,14 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P223" t="n">
         <v>49</v>
+      </c>
+      <c r="Q223" t="b">
+        <v>0</v>
       </c>
       <c r="R223" t="n">
         <v>57</v>
@@ -16307,11 +16973,14 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P224" t="n">
         <v>60</v>
+      </c>
+      <c r="Q224" t="b">
+        <v>0</v>
       </c>
       <c r="R224" t="n">
         <v>57</v>
@@ -16379,11 +17048,14 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P225" t="n">
         <v>34</v>
+      </c>
+      <c r="Q225" t="b">
+        <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>57</v>
@@ -16451,11 +17123,14 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P226" t="n">
         <v>27</v>
+      </c>
+      <c r="Q226" t="b">
+        <v>0</v>
       </c>
       <c r="R226" t="n">
         <v>57</v>
@@ -16523,11 +17198,14 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P227" t="n">
         <v>39</v>
+      </c>
+      <c r="Q227" t="b">
+        <v>0</v>
       </c>
       <c r="R227" t="n">
         <v>57</v>
@@ -16588,6 +17266,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q228" t="b">
+        <v>0</v>
+      </c>
       <c r="R228" t="n">
         <v>57</v>
       </c>
@@ -16654,11 +17335,14 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P229" t="n">
         <v>43</v>
+      </c>
+      <c r="Q229" t="b">
+        <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>57</v>
@@ -16726,11 +17410,14 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P230" t="n">
         <v>63</v>
+      </c>
+      <c r="Q230" t="b">
+        <v>0</v>
       </c>
       <c r="R230" t="n">
         <v>57</v>
@@ -16798,11 +17485,14 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P231" t="n">
         <v>61</v>
+      </c>
+      <c r="Q231" t="b">
+        <v>0</v>
       </c>
       <c r="R231" t="n">
         <v>57</v>
@@ -16870,11 +17560,14 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P232" t="n">
         <v>64</v>
+      </c>
+      <c r="Q232" t="b">
+        <v>1</v>
       </c>
       <c r="R232" t="n">
         <v>57</v>
@@ -16942,11 +17635,14 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P233" t="n">
         <v>39</v>
+      </c>
+      <c r="Q233" t="b">
+        <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>57</v>
@@ -17014,11 +17710,14 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P234" t="n">
         <v>70</v>
+      </c>
+      <c r="Q234" t="b">
+        <v>0</v>
       </c>
       <c r="R234" t="n">
         <v>57</v>
@@ -17086,11 +17785,14 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P235" t="n">
         <v>62</v>
+      </c>
+      <c r="Q235" t="b">
+        <v>0</v>
       </c>
       <c r="R235" t="n">
         <v>57</v>
@@ -17158,11 +17860,14 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P236" t="n">
         <v>49</v>
+      </c>
+      <c r="Q236" t="b">
+        <v>0</v>
       </c>
       <c r="R236" t="n">
         <v>57</v>
@@ -17223,6 +17928,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q237" t="b">
+        <v>0</v>
+      </c>
       <c r="R237" t="n">
         <v>57</v>
       </c>
@@ -17289,11 +17997,14 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P238" t="n">
         <v>57</v>
+      </c>
+      <c r="Q238" t="b">
+        <v>0</v>
       </c>
       <c r="R238" t="n">
         <v>57</v>
@@ -17361,11 +18072,14 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P239" t="n">
         <v>37</v>
+      </c>
+      <c r="Q239" t="b">
+        <v>0</v>
       </c>
       <c r="R239" t="n">
         <v>57</v>
@@ -17433,11 +18147,14 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P240" t="n">
         <v>42</v>
+      </c>
+      <c r="Q240" t="b">
+        <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>57</v>
@@ -17505,11 +18222,14 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P241" t="n">
         <v>43</v>
+      </c>
+      <c r="Q241" t="b">
+        <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>57</v>
@@ -17577,11 +18297,14 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P242" t="n">
         <v>58</v>
+      </c>
+      <c r="Q242" t="b">
+        <v>0</v>
       </c>
       <c r="R242" t="n">
         <v>57</v>
@@ -17649,11 +18372,14 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P243" t="n">
         <v>35</v>
+      </c>
+      <c r="Q243" t="b">
+        <v>0</v>
       </c>
       <c r="R243" t="n">
         <v>57</v>
@@ -17721,11 +18447,14 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P244" t="n">
         <v>47</v>
+      </c>
+      <c r="Q244" t="b">
+        <v>0</v>
       </c>
       <c r="R244" t="n">
         <v>57</v>
@@ -17793,11 +18522,14 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P245" t="n">
         <v>47</v>
+      </c>
+      <c r="Q245" t="b">
+        <v>0</v>
       </c>
       <c r="R245" t="n">
         <v>57</v>
@@ -17865,11 +18597,14 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P246" t="n">
         <v>64</v>
+      </c>
+      <c r="Q246" t="b">
+        <v>0</v>
       </c>
       <c r="R246" t="n">
         <v>57</v>
@@ -17932,16 +18667,19 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P247" t="n">
         <v>47</v>
+      </c>
+      <c r="Q247" t="b">
+        <v>0</v>
       </c>
       <c r="R247" t="n">
         <v>57</v>
@@ -18004,16 +18742,19 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P248" t="n">
         <v>74</v>
+      </c>
+      <c r="Q248" t="b">
+        <v>0</v>
       </c>
       <c r="R248" t="n">
         <v>57</v>
@@ -18076,16 +18817,19 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P249" t="n">
         <v>59</v>
+      </c>
+      <c r="Q249" t="b">
+        <v>0</v>
       </c>
       <c r="R249" t="n">
         <v>57</v>
@@ -18148,16 +18892,19 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P250" t="n">
         <v>49</v>
+      </c>
+      <c r="Q250" t="b">
+        <v>0</v>
       </c>
       <c r="R250" t="n">
         <v>57</v>
@@ -18218,6 +18965,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q251" t="b">
+        <v>0</v>
+      </c>
       <c r="R251" t="n">
         <v>57</v>
       </c>
@@ -18279,16 +19029,19 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P252" t="n">
         <v>37</v>
+      </c>
+      <c r="Q252" t="b">
+        <v>0</v>
       </c>
       <c r="R252" t="n">
         <v>57</v>
@@ -18351,16 +19104,19 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P253" t="n">
         <v>42</v>
+      </c>
+      <c r="Q253" t="b">
+        <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>57</v>
@@ -18428,11 +19184,14 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P254" t="n">
         <v>49</v>
+      </c>
+      <c r="Q254" t="b">
+        <v>0</v>
       </c>
       <c r="R254" t="n">
         <v>57</v>
@@ -18495,16 +19254,19 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P255" t="n">
         <v>37</v>
+      </c>
+      <c r="Q255" t="b">
+        <v>0</v>
       </c>
       <c r="R255" t="n">
         <v>57</v>
@@ -18567,16 +19329,19 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P256" t="n">
         <v>45</v>
+      </c>
+      <c r="Q256" t="b">
+        <v>0</v>
       </c>
       <c r="R256" t="n">
         <v>57</v>
@@ -18644,11 +19409,14 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P257" t="n">
         <v>42</v>
+      </c>
+      <c r="Q257" t="b">
+        <v>0</v>
       </c>
       <c r="R257" t="n">
         <v>57</v>
@@ -18716,11 +19484,14 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P258" t="n">
         <v>37</v>
+      </c>
+      <c r="Q258" t="b">
+        <v>0</v>
       </c>
       <c r="R258" t="n">
         <v>57</v>
@@ -18788,11 +19559,14 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P259" t="n">
         <v>39</v>
+      </c>
+      <c r="Q259" t="b">
+        <v>0</v>
       </c>
       <c r="R259" t="n">
         <v>57</v>
@@ -18860,11 +19634,14 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P260" t="n">
         <v>42</v>
+      </c>
+      <c r="Q260" t="b">
+        <v>0</v>
       </c>
       <c r="R260" t="n">
         <v>57</v>
@@ -18932,11 +19709,14 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P261" t="n">
         <v>33</v>
+      </c>
+      <c r="Q261" t="b">
+        <v>0</v>
       </c>
       <c r="R261" t="n">
         <v>57</v>
@@ -18997,6 +19777,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q262" t="b">
+        <v>0</v>
+      </c>
       <c r="R262" t="n">
         <v>57</v>
       </c>
@@ -19063,11 +19846,14 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P263" t="n">
         <v>47</v>
+      </c>
+      <c r="Q263" t="b">
+        <v>0</v>
       </c>
       <c r="R263" t="n">
         <v>57</v>
@@ -19130,16 +19916,19 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P264" t="n">
         <v>58</v>
+      </c>
+      <c r="Q264" t="b">
+        <v>0</v>
       </c>
       <c r="R264" t="n">
         <v>57</v>
@@ -19202,16 +19991,19 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P265" t="n">
         <v>68</v>
+      </c>
+      <c r="Q265" t="b">
+        <v>0</v>
       </c>
       <c r="R265" t="n">
         <v>57</v>
@@ -19274,16 +20066,19 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P266" t="n">
         <v>47</v>
+      </c>
+      <c r="Q266" t="b">
+        <v>0</v>
       </c>
       <c r="R266" t="n">
         <v>57</v>
@@ -19346,16 +20141,19 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P267" t="n">
         <v>41</v>
+      </c>
+      <c r="Q267" t="b">
+        <v>0</v>
       </c>
       <c r="R267" t="n">
         <v>57</v>
@@ -19416,6 +20214,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q268" t="b">
+        <v>0</v>
+      </c>
       <c r="R268" t="n">
         <v>57</v>
       </c>
@@ -19477,16 +20278,19 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P269" t="n">
         <v>47</v>
+      </c>
+      <c r="Q269" t="b">
+        <v>0</v>
       </c>
       <c r="R269" t="n">
         <v>57</v>
@@ -19549,16 +20353,19 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P270" t="n">
         <v>48</v>
+      </c>
+      <c r="Q270" t="b">
+        <v>0</v>
       </c>
       <c r="R270" t="n">
         <v>57</v>
@@ -19621,16 +20428,19 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P271" t="n">
         <v>47</v>
+      </c>
+      <c r="Q271" t="b">
+        <v>0</v>
       </c>
       <c r="R271" t="n">
         <v>57</v>
@@ -19693,16 +20503,19 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P272" t="n">
         <v>53</v>
+      </c>
+      <c r="Q272" t="b">
+        <v>0</v>
       </c>
       <c r="R272" t="n">
         <v>57</v>
@@ -19765,16 +20578,19 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P273" t="n">
         <v>35</v>
+      </c>
+      <c r="Q273" t="b">
+        <v>0</v>
       </c>
       <c r="R273" t="n">
         <v>57</v>
@@ -19837,16 +20653,19 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P274" t="n">
         <v>54</v>
+      </c>
+      <c r="Q274" t="b">
+        <v>1</v>
       </c>
       <c r="R274" t="n">
         <v>57</v>
@@ -19909,16 +20728,19 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P275" t="n">
         <v>29</v>
+      </c>
+      <c r="Q275" t="b">
+        <v>0</v>
       </c>
       <c r="R275" t="n">
         <v>57</v>
@@ -19981,16 +20803,19 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P276" t="n">
         <v>36</v>
+      </c>
+      <c r="Q276" t="b">
+        <v>0</v>
       </c>
       <c r="R276" t="n">
         <v>57</v>
@@ -20053,16 +20878,19 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P277" t="n">
         <v>46</v>
+      </c>
+      <c r="Q277" t="b">
+        <v>0</v>
       </c>
       <c r="R277" t="n">
         <v>57</v>
@@ -20125,16 +20953,19 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P278" t="n">
         <v>39</v>
+      </c>
+      <c r="Q278" t="b">
+        <v>0</v>
       </c>
       <c r="R278" t="n">
         <v>57</v>
@@ -20195,6 +21026,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q279" t="b">
+        <v>0</v>
+      </c>
       <c r="R279" t="n">
         <v>57</v>
       </c>
@@ -20256,16 +21090,19 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P280" t="n">
         <v>49</v>
+      </c>
+      <c r="Q280" t="b">
+        <v>0</v>
       </c>
       <c r="R280" t="n">
         <v>57</v>
@@ -20328,16 +21165,19 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P281" t="n">
         <v>66</v>
+      </c>
+      <c r="Q281" t="b">
+        <v>0</v>
       </c>
       <c r="R281" t="n">
         <v>57</v>
@@ -20405,11 +21245,14 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P282" t="n">
         <v>52</v>
+      </c>
+      <c r="Q282" t="b">
+        <v>0</v>
       </c>
       <c r="R282" t="n">
         <v>57</v>
@@ -20472,16 +21315,19 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P283" t="n">
         <v>53</v>
+      </c>
+      <c r="Q283" t="b">
+        <v>0</v>
       </c>
       <c r="R283" t="n">
         <v>57</v>
@@ -20544,16 +21390,19 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P284" t="n">
         <v>63</v>
+      </c>
+      <c r="Q284" t="b">
+        <v>0</v>
       </c>
       <c r="R284" t="n">
         <v>57</v>
@@ -20616,16 +21465,19 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P285" t="n">
         <v>42</v>
+      </c>
+      <c r="Q285" t="b">
+        <v>0</v>
       </c>
       <c r="R285" t="n">
         <v>57</v>
@@ -20688,16 +21540,19 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P286" t="n">
         <v>71</v>
+      </c>
+      <c r="Q286" t="b">
+        <v>0</v>
       </c>
       <c r="R286" t="n">
         <v>57</v>
@@ -20760,16 +21615,19 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P287" t="n">
         <v>59</v>
+      </c>
+      <c r="Q287" t="b">
+        <v>0</v>
       </c>
       <c r="R287" t="n">
         <v>57</v>
@@ -20832,16 +21690,19 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P288" t="n">
         <v>47</v>
+      </c>
+      <c r="Q288" t="b">
+        <v>0</v>
       </c>
       <c r="R288" t="n">
         <v>57</v>
@@ -20902,6 +21763,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q289" t="b">
+        <v>0</v>
+      </c>
       <c r="R289" t="n">
         <v>57</v>
       </c>
@@ -20963,16 +21827,19 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P290" t="n">
         <v>44</v>
+      </c>
+      <c r="Q290" t="b">
+        <v>0</v>
       </c>
       <c r="R290" t="n">
         <v>57</v>
@@ -21035,16 +21902,19 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P291" t="n">
         <v>39</v>
+      </c>
+      <c r="Q291" t="b">
+        <v>0</v>
       </c>
       <c r="R291" t="n">
         <v>57</v>
@@ -21107,16 +21977,19 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P292" t="n">
         <v>42</v>
+      </c>
+      <c r="Q292" t="b">
+        <v>0</v>
       </c>
       <c r="R292" t="n">
         <v>57</v>
@@ -21179,16 +22052,19 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P293" t="n">
         <v>56</v>
+      </c>
+      <c r="Q293" t="b">
+        <v>0</v>
       </c>
       <c r="R293" t="n">
         <v>57</v>
@@ -21251,16 +22127,19 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P294" t="n">
         <v>47</v>
+      </c>
+      <c r="Q294" t="b">
+        <v>0</v>
       </c>
       <c r="R294" t="n">
         <v>57</v>
@@ -21323,16 +22202,19 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P295" t="n">
         <v>49</v>
+      </c>
+      <c r="Q295" t="b">
+        <v>0</v>
       </c>
       <c r="R295" t="n">
         <v>57</v>
@@ -21395,16 +22277,19 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P296" t="n">
         <v>41</v>
+      </c>
+      <c r="Q296" t="b">
+        <v>0</v>
       </c>
       <c r="R296" t="n">
         <v>57</v>
@@ -21467,16 +22352,19 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P297" t="n">
         <v>45</v>
+      </c>
+      <c r="Q297" t="b">
+        <v>0</v>
       </c>
       <c r="R297" t="n">
         <v>57</v>
@@ -21537,6 +22425,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q298" t="b">
+        <v>0</v>
+      </c>
       <c r="R298" t="n">
         <v>57</v>
       </c>
@@ -21598,16 +22489,19 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P299" t="n">
         <v>48</v>
+      </c>
+      <c r="Q299" t="b">
+        <v>0</v>
       </c>
       <c r="R299" t="n">
         <v>57</v>
@@ -21670,16 +22564,19 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P300" t="n">
         <v>33</v>
+      </c>
+      <c r="Q300" t="b">
+        <v>0</v>
       </c>
       <c r="R300" t="n">
         <v>57</v>
@@ -21742,16 +22639,19 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P301" t="n">
         <v>39</v>
+      </c>
+      <c r="Q301" t="b">
+        <v>0</v>
       </c>
       <c r="R301" t="n">
         <v>57</v>
@@ -21814,16 +22714,19 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P302" t="n">
         <v>52</v>
+      </c>
+      <c r="Q302" t="b">
+        <v>0</v>
       </c>
       <c r="R302" t="n">
         <v>57</v>
@@ -21886,16 +22789,19 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P303" t="n">
         <v>61</v>
+      </c>
+      <c r="Q303" t="b">
+        <v>0</v>
       </c>
       <c r="R303" t="n">
         <v>57</v>
@@ -21958,16 +22864,19 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P304" t="n">
         <v>64</v>
+      </c>
+      <c r="Q304" t="b">
+        <v>1</v>
       </c>
       <c r="R304" t="n">
         <v>57</v>
@@ -22030,16 +22939,19 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P305" t="n">
         <v>53</v>
+      </c>
+      <c r="Q305" t="b">
+        <v>0</v>
       </c>
       <c r="R305" t="n">
         <v>57</v>
@@ -22102,16 +23014,19 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P306" t="n">
         <v>34</v>
+      </c>
+      <c r="Q306" t="b">
+        <v>0</v>
       </c>
       <c r="R306" t="n">
         <v>57</v>
@@ -22172,6 +23087,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q307" t="b">
+        <v>0</v>
+      </c>
       <c r="R307" t="n">
         <v>57</v>
       </c>
@@ -22233,16 +23151,19 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P308" t="n">
         <v>42</v>
+      </c>
+      <c r="Q308" t="b">
+        <v>0</v>
       </c>
       <c r="R308" t="n">
         <v>57</v>
@@ -22305,16 +23226,19 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P309" t="n">
         <v>63</v>
+      </c>
+      <c r="Q309" t="b">
+        <v>0</v>
       </c>
       <c r="R309" t="n">
         <v>57</v>
@@ -22377,16 +23301,19 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P310" t="n">
         <v>59</v>
+      </c>
+      <c r="Q310" t="b">
+        <v>0</v>
       </c>
       <c r="R310" t="n">
         <v>57</v>
@@ -22449,16 +23376,19 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P311" t="n">
         <v>60</v>
+      </c>
+      <c r="Q311" t="b">
+        <v>0</v>
       </c>
       <c r="R311" t="n">
         <v>57</v>
@@ -22521,16 +23451,19 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P312" t="n">
         <v>62</v>
+      </c>
+      <c r="Q312" t="b">
+        <v>0</v>
       </c>
       <c r="R312" t="n">
         <v>57</v>
@@ -22593,16 +23526,19 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P313" t="n">
         <v>33</v>
+      </c>
+      <c r="Q313" t="b">
+        <v>0</v>
       </c>
       <c r="R313" t="n">
         <v>57</v>
@@ -22663,6 +23599,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q314" t="b">
+        <v>0</v>
+      </c>
       <c r="R314" t="n">
         <v>57</v>
       </c>
@@ -22724,16 +23663,19 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P315" t="n">
         <v>59</v>
+      </c>
+      <c r="Q315" t="b">
+        <v>0</v>
       </c>
       <c r="R315" t="n">
         <v>57</v>
@@ -22796,16 +23738,19 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P316" t="n">
         <v>69</v>
+      </c>
+      <c r="Q316" t="b">
+        <v>0</v>
       </c>
       <c r="R316" t="n">
         <v>57</v>
@@ -22873,11 +23818,14 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P317" t="n">
         <v>63</v>
+      </c>
+      <c r="Q317" t="b">
+        <v>0</v>
       </c>
       <c r="R317" t="n">
         <v>57</v>
@@ -22940,16 +23888,19 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P318" t="n">
         <v>32</v>
+      </c>
+      <c r="Q318" t="b">
+        <v>0</v>
       </c>
       <c r="R318" t="n">
         <v>57</v>
@@ -23012,16 +23963,19 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P319" t="n">
         <v>39</v>
+      </c>
+      <c r="Q319" t="b">
+        <v>0</v>
       </c>
       <c r="R319" t="n">
         <v>57</v>
@@ -23084,16 +24038,19 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P320" t="n">
         <v>55</v>
+      </c>
+      <c r="Q320" t="b">
+        <v>0</v>
       </c>
       <c r="R320" t="n">
         <v>57</v>
@@ -23156,16 +24113,19 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P321" t="n">
         <v>66</v>
+      </c>
+      <c r="Q321" t="b">
+        <v>0</v>
       </c>
       <c r="R321" t="n">
         <v>57</v>
@@ -23233,11 +24193,14 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P322" t="n">
         <v>48</v>
+      </c>
+      <c r="Q322" t="b">
+        <v>0</v>
       </c>
       <c r="R322" t="n">
         <v>57</v>
@@ -23300,16 +24263,19 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P323" t="n">
         <v>36</v>
+      </c>
+      <c r="Q323" t="b">
+        <v>0</v>
       </c>
       <c r="R323" t="n">
         <v>57</v>
@@ -23372,16 +24338,19 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>F</t>
         </is>
       </c>
       <c r="P324" t="n">
         <v>58</v>
+      </c>
+      <c r="Q324" t="b">
+        <v>0</v>
       </c>
       <c r="R324" t="n">
         <v>57</v>
@@ -23449,11 +24418,14 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P325" t="n">
         <v>57</v>
+      </c>
+      <c r="Q325" t="b">
+        <v>0</v>
       </c>
       <c r="R325" t="n">
         <v>57</v>

--- a/static/data/exports/Retro_PY_AE_2026.xlsx
+++ b/static/data/exports/Retro_PY_AE_2026.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10637,11 +10637,11 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1961975</v>
+        <v>1961974</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Egambaram Gandhi</t>
+          <t>P. Vijayabhaasgar</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Egambaram Gandhi</t>
+          <t>P. Vijayabhaasgar</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10689,11 +10689,11 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="Q139" t="b">
         <v>0</v>
@@ -10712,11 +10712,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1961974</v>
+        <v>1961975</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>P. Vijayabhaasgar</t>
+          <t>Egambaram Gandhi</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>P. Vijayabhaasgar</t>
+          <t>Egambaram Gandhi</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10764,11 +10764,11 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q140" t="b">
         <v>0</v>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11537,7 +11537,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>14373</v>
+        <v>22265</v>
       </c>
       <c r="E151" t="n">
         <v>9099</v>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>14373</v>
+        <v>22265</v>
       </c>
       <c r="E160" t="n">
         <v>300</v>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16161,7 +16161,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17198,7 +17198,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17710,7 +17710,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21170,7 +21170,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21545,7 +21545,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21695,7 +21695,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22357,7 +22357,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23381,7 +23381,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24193,7 +24193,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24216,20 +24216,20 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>1962159</v>
+        <v>1962158</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Janipalli Venkanna Babu</t>
+          <t>Malladi Udaya Lakshmi</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>NADLMMKLK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>34077</v>
+        <v>22267</v>
       </c>
       <c r="E323" t="n">
         <v>9</v>
@@ -24253,12 +24253,12 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Janipalli Venkanna Babu</t>
+          <t>Malladi Udaya Lakshmi</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>NADLMMKLK</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24268,11 +24268,11 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P323" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="Q323" t="b">
         <v>0</v>
@@ -24291,20 +24291,20 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>1962158</v>
+        <v>1962159</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Malladi Udaya Lakshmi</t>
+          <t>Janipalli Venkanna Babu</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADLMMKLK</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>22267</v>
+        <v>34077</v>
       </c>
       <c r="E324" t="n">
         <v>9</v>
@@ -24328,12 +24328,12 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Malladi Udaya Lakshmi</t>
+          <t>Janipalli Venkanna Babu</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADLMMKLK</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24343,11 +24343,11 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="Q324" t="b">
         <v>0</v>
@@ -24418,7 +24418,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
